--- a/facebook_comments_data.xlsx
+++ b/facebook_comments_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>message</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>post_description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -471,6 +476,11 @@
           <t>dsfsdfsds fdsdgfdsg sfgdfhd</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>complient</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -493,6 +503,11 @@
           <t>gfdgfdgdfgdfgdfg</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>complient</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -515,6 +530,11 @@
           <t>rthfhfh</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>complient</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -537,6 +557,11 @@
           <t>xzcvxvxcbcv</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>complient</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -559,6 +584,11 @@
           <t>dfdsfdsfdsfdsfsdfsfd</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>complient</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -581,6 +611,11 @@
           <t>hjvjjhvjjggvggjvkgkb</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>complient</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -603,6 +638,11 @@
           <t>vvbcbcvbcvbcvbcv</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>complient</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -625,6 +665,11 @@
           <t>akash</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>complient</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -647,6 +692,11 @@
           <t>I prefer kling ai</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>complient</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -669,6 +719,11 @@
           <t>aaaaaa</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>complient</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -691,6 +746,11 @@
           <t>hello</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>complient</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -713,6 +773,11 @@
           <t>god</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>complient</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -733,6 +798,11 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>hello wassup</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>complient</t>
         </is>
       </c>
     </row>
